--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N48_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N48_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.42084098416397</v>
+        <v>2.018386659926645</v>
       </c>
       <c r="D2" t="n">
-        <v>12.690054339079</v>
+        <v>2.062133830100338</v>
       </c>
       <c r="E2" t="n">
-        <v>6.432675890565921</v>
+        <v>1.045309832216962</v>
       </c>
       <c r="F2" t="n">
-        <v>6.137797554082201</v>
+        <v>0.9973921025383576</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>28.12650885419612</v>
+        <v>4.57055768880687</v>
       </c>
       <c r="D3" t="n">
-        <v>27.66718056718199</v>
+        <v>4.495916842167073</v>
       </c>
       <c r="E3" t="n">
-        <v>6.432675890565921</v>
+        <v>1.045309832216962</v>
       </c>
       <c r="F3" t="n">
-        <v>6.137797554082201</v>
+        <v>0.9973921025383576</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>21.37182498906394</v>
+        <v>3.472921560722891</v>
       </c>
       <c r="D4" t="n">
-        <v>21.31474338261221</v>
+        <v>3.463645799674484</v>
       </c>
       <c r="E4" t="n">
-        <v>6.432675890565921</v>
+        <v>1.045309832216962</v>
       </c>
       <c r="F4" t="n">
-        <v>6.137797554082201</v>
+        <v>0.9973921025383576</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
